--- a/data/nzd0168/nzd0168.xlsx
+++ b/data/nzd0168/nzd0168.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G382"/>
+  <dimension ref="A1:G385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10740,6 +10740,87 @@
       <c r="G382" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>353.13</v>
+      </c>
+      <c r="C383" t="n">
+        <v>349.62</v>
+      </c>
+      <c r="D383" t="n">
+        <v>355.79</v>
+      </c>
+      <c r="E383" t="n">
+        <v>347.55</v>
+      </c>
+      <c r="F383" t="n">
+        <v>356.25</v>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>351.49</v>
+      </c>
+      <c r="C384" t="n">
+        <v>348.75</v>
+      </c>
+      <c r="D384" t="n">
+        <v>354.01</v>
+      </c>
+      <c r="E384" t="n">
+        <v>347.76</v>
+      </c>
+      <c r="F384" t="n">
+        <v>355.19</v>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>352.22</v>
+      </c>
+      <c r="C385" t="n">
+        <v>349.27</v>
+      </c>
+      <c r="D385" t="n">
+        <v>353.85</v>
+      </c>
+      <c r="E385" t="n">
+        <v>347.45</v>
+      </c>
+      <c r="F385" t="n">
+        <v>355.67</v>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -10754,7 +10835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B400"/>
+  <dimension ref="A1:B403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14757,6 +14838,36 @@
       </c>
       <c r="B400" t="n">
         <v>-0.55</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>0.36</v>
       </c>
     </row>
   </sheetData>
@@ -14925,28 +15036,28 @@
         <v>0.055</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09063946059707843</v>
+        <v>0.08666709999108674</v>
       </c>
       <c r="J2" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="K2" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01685073489985345</v>
+        <v>0.01566473495440424</v>
       </c>
       <c r="M2" t="n">
-        <v>3.901153563790137</v>
+        <v>3.892426130779629</v>
       </c>
       <c r="N2" t="n">
-        <v>26.519428756305</v>
+        <v>26.36576218037835</v>
       </c>
       <c r="O2" t="n">
-        <v>5.149701812367877</v>
+        <v>5.134760187231567</v>
       </c>
       <c r="P2" t="n">
-        <v>352.3951093193738</v>
+        <v>352.4382517460112</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15003,28 +15114,28 @@
         <v>0.0852</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1773391626547616</v>
+        <v>0.1773890489705002</v>
       </c>
       <c r="J3" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="K3" t="n">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0620986795070021</v>
+        <v>0.06315979402474159</v>
       </c>
       <c r="M3" t="n">
-        <v>4.012186776003776</v>
+        <v>3.983188493375228</v>
       </c>
       <c r="N3" t="n">
-        <v>26.03510165012638</v>
+        <v>25.83219695382045</v>
       </c>
       <c r="O3" t="n">
-        <v>5.102460352626601</v>
+        <v>5.082538436039657</v>
       </c>
       <c r="P3" t="n">
-        <v>344.3976280409665</v>
+        <v>344.3970847169483</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15081,28 +15192,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2382859502798125</v>
+        <v>0.2434136834710592</v>
       </c>
       <c r="J4" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="K4" t="n">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07602752673879387</v>
+        <v>0.08018739789151996</v>
       </c>
       <c r="M4" t="n">
-        <v>4.840946682258646</v>
+        <v>4.827945520736628</v>
       </c>
       <c r="N4" t="n">
-        <v>37.82337092391187</v>
+        <v>37.61543843234419</v>
       </c>
       <c r="O4" t="n">
-        <v>6.150070806414498</v>
+        <v>6.133142622860175</v>
       </c>
       <c r="P4" t="n">
-        <v>344.8405397609359</v>
+        <v>344.7845101996081</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15159,28 +15270,28 @@
         <v>0.1843</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2349867021396545</v>
+        <v>0.2373288706805332</v>
       </c>
       <c r="J5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="K5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06734314234202898</v>
+        <v>0.06969764886437368</v>
       </c>
       <c r="M5" t="n">
-        <v>5.283264902322767</v>
+        <v>5.253692607781564</v>
       </c>
       <c r="N5" t="n">
-        <v>42.31009598376554</v>
+        <v>41.99706528226977</v>
       </c>
       <c r="O5" t="n">
-        <v>6.504621125305111</v>
+        <v>6.480514276064035</v>
       </c>
       <c r="P5" t="n">
-        <v>339.7357999393083</v>
+        <v>339.7103658399382</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15237,28 +15348,28 @@
         <v>0.0422</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1447083629002766</v>
+        <v>-0.1519397167137131</v>
       </c>
       <c r="J6" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="K6" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002928669805338679</v>
+        <v>0.0032833880840899</v>
       </c>
       <c r="M6" t="n">
-        <v>15.00689093477098</v>
+        <v>14.91605956909123</v>
       </c>
       <c r="N6" t="n">
-        <v>386.8892831361396</v>
+        <v>383.9978869250858</v>
       </c>
       <c r="O6" t="n">
-        <v>19.66950134436915</v>
+        <v>19.59586402598992</v>
       </c>
       <c r="P6" t="n">
-        <v>364.1891157629049</v>
+        <v>364.2688641946312</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15296,7 +15407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G382"/>
+  <dimension ref="A1:G385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29409,6 +29520,117 @@
         </is>
       </c>
     </row>
+    <row r="383">
+      <c r="A383" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>-36.76833265135506,175.74968665203124</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>-36.76902593864851,175.74941891568076</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>-36.769748802211794,175.74934652211195</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>-36.77046507331796,175.7491478103733</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>-36.771169410611854,175.74927117435644</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>-36.76832918196196,175.74966880288304</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>-36.76902448322531,175.74940934386328</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>-36.769746924447475,175.7493267286445</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>-36.77046512159579,175.74915016099337</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>-36.77116988122658,175.74925931977245</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>-36.76833072626532,175.74967674793055</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>-36.76902535313352,175.74941506494955</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>-36.7697467556595,175.74932494945645</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>-36.770465050328504,175.74914669103038</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>-36.771169668118176,175.74926468788595</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0168/nzd0168.xlsx
+++ b/data/nzd0168/nzd0168.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G385"/>
+  <dimension ref="A1:G386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10819,6 +10819,33 @@
         <v>355.67</v>
       </c>
       <c r="G385" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>355.02</v>
+      </c>
+      <c r="C386" t="n">
+        <v>349.46</v>
+      </c>
+      <c r="D386" t="n">
+        <v>353.27</v>
+      </c>
+      <c r="E386" t="n">
+        <v>347.69</v>
+      </c>
+      <c r="F386" t="n">
+        <v>356.06</v>
+      </c>
+      <c r="G386" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -10835,7 +10862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B403"/>
+  <dimension ref="A1:B404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14867,6 +14894,16 @@
         </is>
       </c>
       <c r="B403" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
         <v>0.36</v>
       </c>
     </row>
@@ -15036,28 +15073,28 @@
         <v>0.055</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08666709999108674</v>
+        <v>0.08679103733560756</v>
       </c>
       <c r="J2" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K2" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01566473495440424</v>
+        <v>0.01579817395720939</v>
       </c>
       <c r="M2" t="n">
-        <v>3.892426130779629</v>
+        <v>3.88287455269011</v>
       </c>
       <c r="N2" t="n">
-        <v>26.36576218037835</v>
+        <v>26.29742854772274</v>
       </c>
       <c r="O2" t="n">
-        <v>5.134760187231567</v>
+        <v>5.128101846465487</v>
       </c>
       <c r="P2" t="n">
-        <v>352.4382517460112</v>
+        <v>352.4369021734508</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15114,28 +15151,28 @@
         <v>0.0852</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1773890489705002</v>
+        <v>0.1775249851291758</v>
       </c>
       <c r="J3" t="n">
+        <v>385</v>
+      </c>
+      <c r="K3" t="n">
         <v>384</v>
       </c>
-      <c r="K3" t="n">
-        <v>383</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.06315979402474159</v>
+        <v>0.06359408450700665</v>
       </c>
       <c r="M3" t="n">
-        <v>3.983188493375228</v>
+        <v>3.973263555281191</v>
       </c>
       <c r="N3" t="n">
-        <v>25.83219695382045</v>
+        <v>25.76510226128289</v>
       </c>
       <c r="O3" t="n">
-        <v>5.082538436039657</v>
+        <v>5.075933634444297</v>
       </c>
       <c r="P3" t="n">
-        <v>344.3970847169483</v>
+        <v>344.3955950776103</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15192,28 +15229,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2434136834710592</v>
+        <v>0.2444012673715101</v>
       </c>
       <c r="J4" t="n">
+        <v>385</v>
+      </c>
+      <c r="K4" t="n">
         <v>384</v>
       </c>
-      <c r="K4" t="n">
-        <v>383</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.08018739789151996</v>
+        <v>0.08119926812840439</v>
       </c>
       <c r="M4" t="n">
-        <v>4.827945520736628</v>
+        <v>4.820200166013674</v>
       </c>
       <c r="N4" t="n">
-        <v>37.61543843234419</v>
+        <v>37.52680552880642</v>
       </c>
       <c r="O4" t="n">
-        <v>6.133142622860175</v>
+        <v>6.12591262823805</v>
       </c>
       <c r="P4" t="n">
-        <v>344.7845101996081</v>
+        <v>344.7736878853544</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15270,28 +15307,28 @@
         <v>0.1843</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2373288706805332</v>
+        <v>0.2381356265947387</v>
       </c>
       <c r="J5" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K5" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06969764886437368</v>
+        <v>0.07050610249826161</v>
       </c>
       <c r="M5" t="n">
-        <v>5.253692607781564</v>
+        <v>5.244048869666314</v>
       </c>
       <c r="N5" t="n">
-        <v>41.99706528226977</v>
+        <v>41.89428978197486</v>
       </c>
       <c r="O5" t="n">
-        <v>6.480514276064035</v>
+        <v>6.472579839752837</v>
       </c>
       <c r="P5" t="n">
-        <v>339.7103658399382</v>
+        <v>339.7015809523083</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15348,28 +15385,28 @@
         <v>0.0422</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1519397167137131</v>
+        <v>-0.1540903201715057</v>
       </c>
       <c r="J6" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K6" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0032833880840899</v>
+        <v>0.003395868316616535</v>
       </c>
       <c r="M6" t="n">
-        <v>14.91605956909123</v>
+        <v>14.88518503383086</v>
       </c>
       <c r="N6" t="n">
-        <v>383.9978869250858</v>
+        <v>383.033721703756</v>
       </c>
       <c r="O6" t="n">
-        <v>19.59586402598992</v>
+        <v>19.57124732110235</v>
       </c>
       <c r="P6" t="n">
-        <v>364.2688641946312</v>
+        <v>364.2926446042596</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15407,7 +15444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G385"/>
+  <dimension ref="A1:G386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29631,6 +29668,43 @@
         </is>
       </c>
     </row>
+    <row r="386">
+      <c r="A386" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>-36.768336649615655,175.749707222088</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>-36.76902567098455,175.7494171553465</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>-36.76974614380289,175.74931849989983</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>-36.770465105503185,175.74914937745334</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>-36.7711694949674,175.7492690494782</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
